--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/Swint_2/SwinT2+50T+50EP+optim_purn/params_vs_psnr_analysis/SwinT_hutcn_hyperopt_study_3cols.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/Swint_2/SwinT2+50T+50EP+optim_purn/params_vs_psnr_analysis/SwinT_hutcn_hyperopt_study_3cols.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +441,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>FLOPs (G) @ 48x48</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>PSNR (dB)</t>
         </is>
       </c>
@@ -453,6 +458,9 @@
         <v>686598</v>
       </c>
       <c r="C2" t="n">
+        <v>1.708990668</v>
+      </c>
+      <c r="D2" t="n">
         <v>27.70468902587891</v>
       </c>
     </row>
@@ -464,6 +472,9 @@
         <v>728622</v>
       </c>
       <c r="C3" t="n">
+        <v>1.598429376</v>
+      </c>
+      <c r="D3" t="n">
         <v>28.06456909179688</v>
       </c>
     </row>
@@ -475,6 +486,9 @@
         <v>734194</v>
       </c>
       <c r="C4" t="n">
+        <v>1.697519808</v>
+      </c>
+      <c r="D4" t="n">
         <v>28.08228149414062</v>
       </c>
     </row>
@@ -486,6 +500,9 @@
         <v>408546</v>
       </c>
       <c r="C5" t="n">
+        <v>1.009748736</v>
+      </c>
+      <c r="D5" t="n">
         <v>29.60862808227539</v>
       </c>
     </row>
@@ -497,6 +514,9 @@
         <v>887138</v>
       </c>
       <c r="C6" t="n">
+        <v>1.949669568</v>
+      </c>
+      <c r="D6" t="n">
         <v>30.42318077087402</v>
       </c>
     </row>
@@ -508,6 +528,9 @@
         <v>1124502</v>
       </c>
       <c r="C7" t="n">
+        <v>2.54966238</v>
+      </c>
+      <c r="D7" t="n">
         <v>28.12018013000488</v>
       </c>
     </row>
@@ -519,6 +542,9 @@
         <v>515210</v>
       </c>
       <c r="C8" t="n">
+        <v>1.14190776</v>
+      </c>
+      <c r="D8" t="n">
         <v>27.86694107055664</v>
       </c>
     </row>
@@ -530,6 +556,9 @@
         <v>412778</v>
       </c>
       <c r="C9" t="n">
+        <v>1.009748736</v>
+      </c>
+      <c r="D9" t="n">
         <v>27.85125541687012</v>
       </c>
     </row>
@@ -541,6 +570,9 @@
         <v>1422442</v>
       </c>
       <c r="C10" t="n">
+        <v>3.006802944</v>
+      </c>
+      <c r="D10" t="n">
         <v>30.29258995056152</v>
       </c>
     </row>
@@ -552,6 +584,9 @@
         <v>514578</v>
       </c>
       <c r="C11" t="n">
+        <v>1.08292536</v>
+      </c>
+      <c r="D11" t="n">
         <v>29.39376831054688</v>
       </c>
     </row>
@@ -563,6 +598,9 @@
         <v>1422442</v>
       </c>
       <c r="C12" t="n">
+        <v>3.006802944</v>
+      </c>
+      <c r="D12" t="n">
         <v>30.48270034790039</v>
       </c>
     </row>
@@ -574,6 +612,9 @@
         <v>1098510</v>
       </c>
       <c r="C13" t="n">
+        <v>2.32969464</v>
+      </c>
+      <c r="D13" t="n">
         <v>30.41798439025879</v>
       </c>
     </row>
@@ -585,6 +626,9 @@
         <v>1209994</v>
       </c>
       <c r="C14" t="n">
+        <v>2.61096696</v>
+      </c>
+      <c r="D14" t="n">
         <v>30.41100616455078</v>
       </c>
     </row>
@@ -596,6 +640,9 @@
         <v>577078</v>
       </c>
       <c r="C15" t="n">
+        <v>1.23369912</v>
+      </c>
+      <c r="D15" t="n">
         <v>30.20738945007324</v>
       </c>
     </row>
@@ -607,6 +654,9 @@
         <v>1041854</v>
       </c>
       <c r="C16" t="n">
+        <v>2.268305676</v>
+      </c>
+      <c r="D16" t="n">
         <v>30.37266540527344</v>
       </c>
     </row>
@@ -618,6 +668,9 @@
         <v>1098510</v>
       </c>
       <c r="C17" t="n">
+        <v>2.32969464</v>
+      </c>
+      <c r="D17" t="n">
         <v>30.41156883239746</v>
       </c>
     </row>
@@ -629,6 +682,9 @@
         <v>1422442</v>
       </c>
       <c r="C18" t="n">
+        <v>3.006802944</v>
+      </c>
+      <c r="D18" t="n">
         <v>30.42910919189453</v>
       </c>
     </row>
@@ -640,6 +696,9 @@
         <v>1422442</v>
       </c>
       <c r="C19" t="n">
+        <v>3.006802944</v>
+      </c>
+      <c r="D19" t="n">
         <v>30.30375938415527</v>
       </c>
     </row>
@@ -651,6 +710,9 @@
         <v>1098510</v>
       </c>
       <c r="C20" t="n">
+        <v>2.32969464</v>
+      </c>
+      <c r="D20" t="n">
         <v>30.42768478393555</v>
       </c>
     </row>
@@ -662,6 +724,9 @@
         <v>1422442</v>
       </c>
       <c r="C21" t="n">
+        <v>3.006802944</v>
+      </c>
+      <c r="D21" t="n">
         <v>30.47668342590332</v>
       </c>
     </row>
@@ -673,6 +738,9 @@
         <v>1422442</v>
       </c>
       <c r="C22" t="n">
+        <v>3.006802944</v>
+      </c>
+      <c r="D22" t="n">
         <v>30.43728790283203</v>
       </c>
     </row>
@@ -684,6 +752,9 @@
         <v>1422442</v>
       </c>
       <c r="C23" t="n">
+        <v>3.006802944</v>
+      </c>
+      <c r="D23" t="n">
         <v>30.43879432678223</v>
       </c>
     </row>
@@ -695,6 +766,9 @@
         <v>1422442</v>
       </c>
       <c r="C24" t="n">
+        <v>3.006802944</v>
+      </c>
+      <c r="D24" t="n">
         <v>30.42079658508301</v>
       </c>
     </row>
@@ -706,6 +780,9 @@
         <v>1422442</v>
       </c>
       <c r="C25" t="n">
+        <v>3.006802944</v>
+      </c>
+      <c r="D25" t="n">
         <v>30.3994270324707</v>
       </c>
     </row>
@@ -717,6 +794,9 @@
         <v>1422442</v>
       </c>
       <c r="C26" t="n">
+        <v>3.006802944</v>
+      </c>
+      <c r="D26" t="n">
         <v>30.46254844665527</v>
       </c>
     </row>
@@ -728,6 +808,9 @@
         <v>1457770</v>
       </c>
       <c r="C27" t="n">
+        <v>3.346541568</v>
+      </c>
+      <c r="D27" t="n">
         <v>30.46813545227051</v>
       </c>
     </row>
